--- a/output/pdf_financials_xlsx/NEXT.xlsx
+++ b/output/pdf_financials_xlsx/NEXT.xlsx
@@ -1069,7 +1069,7 @@
         <v>-1.633713</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.999358</v>
+        <v>-3.999358</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-2.784822</v>
@@ -1273,7 +1273,7 @@
         <v>-1.633713</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.999358</v>
+        <v>-3.999358</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-2.784822</v>
@@ -1393,7 +1393,7 @@
         <v>-1.633713</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.999358</v>
+        <v>-3.999358</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-2.784822</v>
@@ -1559,7 +1559,7 @@
         <v>-1.633713</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.999358</v>
+        <v>-3.999358</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.784822</v>
@@ -1639,7 +1639,7 @@
         <v>-1.577111</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.021269</v>
+        <v>-3.977447</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.784822</v>
@@ -1739,7 +1739,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -47337,7 +47337,7 @@
         </is>
       </c>
       <c r="G590" s="5" t="n">
-        <v>3.999358</v>
+        <v>-3.999358</v>
       </c>
       <c r="H590" s="5" t="n">
         <v>-2.784822</v>

--- a/output/pdf_financials_xlsx/NEXT.xlsx
+++ b/output/pdf_financials_xlsx/NEXT.xlsx
@@ -809,19 +809,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.629817</v>
+        <v>6.927557</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.811704</v>
+        <v>2.408778</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.770397</v>
+        <v>3.979087</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.904054</v>
+        <v>2.841695</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.220394</v>
+        <v>3.284036</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.423353</v>
@@ -836,7 +836,7 @@
         <v>0.355703</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>8.753648999999999</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>0</v>
@@ -921,13 +921,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000104</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000191</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.123869</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>-1.15684</v>
@@ -1571,13 +1571,13 @@
         <v>-0.977635</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-41.960484</v>
+        <v>-41.96038</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>16.120203</v>
+        <v>16.120394</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-11.678687</v>
+        <v>-11.554818</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-7.596809</v>
@@ -1651,13 +1651,13 @@
         <v>-0.977635</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-41.960484</v>
+        <v>-41.96038</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>16.120203</v>
+        <v>16.120394</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-11.678687</v>
+        <v>-11.554818</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-7.596809</v>
@@ -36283,7 +36283,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -36705,7 +36705,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="L438" s="5" t="n">
-        <v>-16.120203</v>
+        <v>16.120203</v>
       </c>
       <c r="M438" s="5" t="n">
         <v>11.678687</v>
@@ -40832,7 +40832,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -40905,7 +40905,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -46980,7 +46980,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E585" s="5" t="n">
@@ -48528,7 +48528,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">

--- a/output/pdf_financials_xlsx/NEXT.xlsx
+++ b/output/pdf_financials_xlsx/NEXT.xlsx
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.393855</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.198322</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
         <v>16.120394</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-11.554818</v>
+        <v>-11.160963</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-7.596809</v>
+        <v>-7.398487</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-22.592213</v>
@@ -4529,10 +4529,10 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.393855</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.198322</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -17646,7 +17646,11 @@
           <t>Depreciation of property, plant and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NEXT.xlsx
+++ b/output/pdf_financials_xlsx/NEXT.xlsx
@@ -3086,10 +3086,10 @@
         <v>0.817265</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>1.22017</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>2.79191</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>0</v>
@@ -3206,13 +3206,13 @@
         <v>1.0474</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>1.794424</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>1.681218</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>3.087594</v>
       </c>
     </row>
     <row r="68">
@@ -3314,25 +3314,25 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.005339</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.010679</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.005254</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.298093</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>10.20937</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>18.797929</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>7.428877</v>
       </c>
     </row>
     <row r="71">
@@ -3354,25 +3354,25 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.005339</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.022115</v>
+        <v>0.032794</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.005254</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.298093</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>10.20937</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>18.797929</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>7.428877</v>
       </c>
     </row>
     <row r="72">
@@ -3514,25 +3514,25 @@
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.51527</v>
+        <v>0.509931</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.456936</v>
+        <v>0.446257</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>46.1248</v>
+        <v>46.119546</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>22.468266</v>
+        <v>22.170173</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>4.887784</v>
+        <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>5.442879</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>18.792726</v>
+        <v>11.363849</v>
       </c>
     </row>
     <row r="76">
@@ -3729,38 +3729,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="3" t="n">
+        <v>-0.008017888947958058</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>-0.02428575821202351</v>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.03601298461700651</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>-0.0002009461834452778</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>-0.09727740865955697</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.4051026240643824</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.3594043852624603</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.1812509666247986</v>
       </c>
     </row>
     <row r="81">
@@ -4806,16 +4794,16 @@
         <v>0</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.31574</v>
       </c>
       <c r="J107" s="3" t="n">
         <v>0.5140479999999999</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0.334411</v>
+        <v>0.201055</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>-0.108911</v>
       </c>
     </row>
     <row r="108">
@@ -5105,10 +5093,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.061847</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.00387</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -6680,7 +6668,11 @@
           <t>Current portion of lease obligations (note 11)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -7092,7 +7084,11 @@
           <t>Lease obligations (note 11)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -8135,7 +8131,11 @@
           <t>Current portion of lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -8413,7 +8413,11 @@
           <t>Lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -9192,7 +9196,11 @@
           <t>Current portion of lease obligations (note 6)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -9472,7 +9480,11 @@
           <t>Lease obligations (note 6)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -10464,7 +10476,11 @@
           <t>Current portion of lease obligations (note 9)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -10736,7 +10752,11 @@
           <t>Lease obligations (note 9)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -12071,7 +12091,11 @@
           <t>Current portion of lease obligations (note</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -16043,7 +16067,11 @@
           <t>Share-based compensation expense (note 21)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -19815,7 +19843,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -31049,7 +31081,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E358" s="5" t="n">
         <v>0.061847</v>
       </c>
